--- a/reports/reporte_2026_03_datos.xlsx
+++ b/reports/reporte_2026_03_datos.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
   <si>
     <t>Año</t>
   </si>
@@ -26,22 +26,22 @@
     <t>Semana</t>
   </si>
   <si>
-    <t>Fecha</t>
+    <t>Fecha_visita</t>
   </si>
   <si>
     <t>Jobs</t>
   </si>
   <si>
-    <t>Centros educativos</t>
-  </si>
-  <si>
-    <t>Distrito</t>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Provincia</t>
   </si>
   <si>
     <t>Hallazgos</t>
   </si>
   <si>
-    <t>Comentarios</t>
+    <t>Observaciones</t>
   </si>
   <si>
     <t>Estado</t>
@@ -53,10 +53,16 @@
     <t>Modelos</t>
   </si>
   <si>
-    <t>Estatus de UPS</t>
+    <t>UPS_estado</t>
   </si>
   <si>
     <t>Tipo de trabajo</t>
+  </si>
+  <si>
+    <t>DHCP_saturacion</t>
+  </si>
+  <si>
+    <t>Uptime</t>
   </si>
   <si>
     <t>March</t>
@@ -175,10 +181,10 @@
     <t>Dell N1524 + Dell N1524</t>
   </si>
   <si>
-    <t>Operativo</t>
-  </si>
-  <si>
-    <t>Averiado</t>
+    <t>operativo</t>
+  </si>
+  <si>
+    <t>averiado</t>
   </si>
   <si>
     <t>Mantenimiento preventivo</t>
@@ -187,25 +193,25 @@
     <t>Incidente detectado en NOC</t>
   </si>
   <si>
-    <t>Nombre de centro</t>
+    <t>Fecha</t>
   </si>
   <si>
     <t>Ubicación de equipos averiados</t>
   </si>
   <si>
-    <t>Dispositivo</t>
-  </si>
-  <si>
-    <t>Serie anteri0r</t>
-  </si>
-  <si>
-    <t>Serie nueva</t>
-  </si>
-  <si>
-    <t>Razón de cierre</t>
-  </si>
-  <si>
-    <t>Técnico</t>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>Serie_anterior</t>
+  </si>
+  <si>
+    <t>Serie_nueva</t>
+  </si>
+  <si>
+    <t>Motivo</t>
+  </si>
+  <si>
+    <t>Tecnico</t>
   </si>
   <si>
     <t>Job</t>
@@ -550,10 +556,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,13 +602,19 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -611,39 +623,45 @@
         <v>46083</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -652,39 +670,45 @@
         <v>46083</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O3">
+        <v>33</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -693,39 +717,45 @@
         <v>46083</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -734,39 +764,45 @@
         <v>46083</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -775,39 +811,45 @@
         <v>46083</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -816,39 +858,45 @@
         <v>46083</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -857,39 +905,45 @@
         <v>46083</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K8">
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -898,39 +952,45 @@
         <v>46083</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -939,39 +999,45 @@
         <v>46083</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>2026</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -980,39 +1046,45 @@
         <v>46083</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>56</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -1021,39 +1093,45 @@
         <v>46084</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>2026</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -1062,39 +1140,45 @@
         <v>46084</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>2026</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1103,31 +1187,37 @@
         <v>46084</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K14">
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N14" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1145,37 +1235,37 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
